--- a/Test_Input/MO2/July/UE/REFACTORED_2. POS by Channel - Uber 2026-07.xlsx
+++ b/Test_Input/MO2/July/UE/REFACTORED_2. POS by Channel - Uber 2026-07.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arthu\Documents\Work\fohboh-sentry\Test_Input\MO2\July\UE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90AF36B1-13CA-4627-AEBA-8ACC64AAF647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BC6B74-E48A-4EA8-A47D-57EA64BC1D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="1695" windowWidth="24525" windowHeight="15435" xr2:uid="{BD5B72ED-17D2-4F17-B66F-8BD07BA4F606}"/>
+    <workbookView xWindow="25410" yWindow="2325" windowWidth="24525" windowHeight="15435" xr2:uid="{BD5B72ED-17D2-4F17-B66F-8BD07BA4F606}"/>
   </bookViews>
   <sheets>
     <sheet name="REFACTORED_2. POS by Channel - " sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -273,7 +284,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -755,7 +766,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -803,10 +814,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+      <numFmt numFmtId="26" formatCode="hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="26" formatCode="hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -828,7 +839,7 @@
     <sortCondition ref="A1:A48"/>
   </sortState>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{D41C9760-F3A6-4725-91B1-CB645C35B882}" name="BUSINESS_DAY" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D41C9760-F3A6-4725-91B1-CB645C35B882}" name="BUSINESS_DAY" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{771EDCFF-CF3C-4631-B922-57B4DE31874A}" name="CHANNEL"/>
     <tableColumn id="3" xr3:uid="{BDD07D19-632F-49A5-ACEB-6444A04BA9FA}" name="CHECK_COUNT"/>
     <tableColumn id="4" xr3:uid="{9D561977-7577-4190-B4B4-B7447BEF696C}" name="CHECK_NET_AMOUNT"/>
@@ -850,7 +861,7 @@
     <tableColumn id="20" xr3:uid="{DD0CF59B-B602-482A-92E4-C279303A7753}" name="ITEM_UPSOLD_AMOUNT"/>
     <tableColumn id="21" xr3:uid="{84122FCE-C855-4DA1-886D-82C45A75AF2E}" name="NET_SALES"/>
     <tableColumn id="22" xr3:uid="{0F92D4F2-58B6-42D5-A82A-27C410108059}" name="ORDER_COUNT"/>
-    <tableColumn id="23" xr3:uid="{2113FBB4-A5AD-4E9A-9BBF-9639C4AF4374}" name="ORDER_DURATION" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{2113FBB4-A5AD-4E9A-9BBF-9639C4AF4374}" name="ORDER_DURATION" dataDxfId="0"/>
     <tableColumn id="24" xr3:uid="{22444B1B-9F4D-443C-8524-0D257F0B8795}" name="ORDER_NET_AMOUNT"/>
     <tableColumn id="25" xr3:uid="{A7958428-6B8F-42C2-8535-409B5774ECB3}" name="ORDERS_WITH_VOIDS_COUNT"/>
     <tableColumn id="26" xr3:uid="{A2A1908B-C4AF-4559-9FBF-07339F47E713}" name="REFUND_AMOUNT"/>
@@ -1170,8 +1181,8 @@
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="37.140625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="33.85546875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="31.28515625" hidden="1" customWidth="1"/>
